--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -758,8 +758,110 @@
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>c486375d816b4876</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>0.765185</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0.08467381789137385</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:24.994619Z</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ2"/>
+  <autoFilter ref="A1:AJ3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -860,8 +860,212 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>7699c3723032434c</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0.765185</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0.08467381789137385</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:45.187026Z</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>9c971933b2124baf</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.765185</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.08467381789137385</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:43.967259Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ3"/>
+  <autoFilter ref="A1:AJ5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1064,8 +1064,110 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>a68d24f406d64438</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.765185</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.07478252321981427</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:51.807690Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ5"/>
+  <autoFilter ref="A1:AJ6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1166,8 +1166,110 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>36b2e3208ac04421</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.765342</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.07493952321981423</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:20.414393Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ6"/>
+  <autoFilter ref="A1:AJ7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1268,8 +1268,110 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6b5495b7ca4c4aed</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.765342</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.07493952321981423</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:08.752039Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ7"/>
+  <autoFilter ref="A1:AJ8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1370,8 +1370,2782 @@
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>47780f06aa7c45ba</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0f5624a5c49dac316bbc3f3b65cce80e0bd90cd62c044b5542fb487496a95a20</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.765342</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.07493952321981423</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:55:21.301007Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2b28df3d4ff24378</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>c4c53479d60e7fd116280c4ec0788bb856af372afb2da0dd70796fd41ac0b643</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.765342</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.07493952321981423</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:32:13.009975Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>4b83ab6075c9475e</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>b8ad95e67a1d231f7c1456f640a0121faebeb1a345256cde26610e3b0d16a846</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.76539</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.07498752321981428</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:24.177666Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>896e89c652454ddd</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5e8b5549e6d11b9dcbac6eb49f3a77e76991aea746bb335daac8491665679f93</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.76539</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.07498752321981428</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:37.099189Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>c76b6b6f5a3544c4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ef4688382c4ee6d8e018bd4a924ee51ae7b769cd16ec250f3a982232c214864b</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.765423</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.07502052321981423</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:36.301917Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2bc0dab8bb794a14</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>ef4688382c4ee6d8e018bd4a924ee51ae7b769cd16ec250f3a982232c214864b</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.653441</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.08262554935622324</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:42.652252Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>9870c9e3e4944b1a</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>ef4688382c4ee6d8e018bd4a924ee51ae7b769cd16ec250f3a982232c214864b</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.691145</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.0407953496503497</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:43.125785Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>8ca3fec3c67346c1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>277e8ce01a142b955fcbb88803ce8e2dc6066bd902cfb91992d21ffbb6cc05d2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.765423</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.07502052321981423</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:41.653499Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>6ecb16ee2c9f48a6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>277e8ce01a142b955fcbb88803ce8e2dc6066bd902cfb91992d21ffbb6cc05d2</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.653441</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.08262554935622324</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:47.733216Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>4d6ca7998783484f</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0e8fd4abee1c27f6189caf0cd699adcd452fddf10fd5a4f4d1f38a426fe33abc</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.765423</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0.07502052321981423</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:15:59.368273Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>cf800ef37af6490c</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0e8fd4abee1c27f6189caf0cd699adcd452fddf10fd5a4f4d1f38a426fe33abc</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.653441</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.08262554935622324</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:16:05.774167Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>b8cc250cf81142aa</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>60796ce290098d7c637a0d46242fb7778456c6b002f4c9691738e33895096a92</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.765423</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.07502052321981423</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:15.084541Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>c9d30126592d428e</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60796ce290098d7c637a0d46242fb7778456c6b002f4c9691738e33895096a92</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.653441</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.08262554935622324</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:21.615935Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>da0e5c21fcf847ab</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>60796ce290098d7c637a0d46242fb7778456c6b002f4c9691738e33895096a92</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.691145</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.07137313688212932</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:22.234112Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>da059feeb4884739</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>78dfbffa72be7b3f900e8efcb573e890ea39e7d8b945e574740ce9ffc44cb1f6</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.765423</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.07502052321981423</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:41.992193Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2a80c701c4b04203</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>78dfbffa72be7b3f900e8efcb573e890ea39e7d8b945e574740ce9ffc44cb1f6</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.653441</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.08262554935622324</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:48.145602Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>13abea7643aa4028</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>78dfbffa72be7b3f900e8efcb573e890ea39e7d8b945e574740ce9ffc44cb1f6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.691145</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.05085723021582733</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:48.713629Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>3014cbe28d684acd</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>afe2fffd3c666e0d8f9040dcc6dedae587629fd14dee7043c87557d9d9d9e6e5</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.765423</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.14565113688212927</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.637118Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>0.620000</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0.000228</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:06:06.510627Z</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>7ecfec211d104d9a</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>f4c9d842ae83d51ecdd617d3ad4bedb83cab61be2a77bfbce25c2ccd77bbedc0</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.653441</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.06327706557377055</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:22.347194Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>74159d6b5ca14063</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>f4c9d842ae83d51ecdd617d3ad4bedb83cab61be2a77bfbce25c2ccd77bbedc0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.691145</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.08177000000000001</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:22.820493Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>30cf2331411244e4</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>8fb1158b4cb581af4b06bfd1ea53c992872bca99425b27e82f5ba5d2f3e0c0a9</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.653441</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0.06327706557377055</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:31:01.273728Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>b31ec5891d0f4ed7</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>8fb1158b4cb581af4b06bfd1ea53c992872bca99425b27e82f5ba5d2f3e0c0a9</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.691145</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.08177000000000001</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:31:01.788915Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>d6f1e1a8b1434513</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>0498800784d6eac428ef81724493d635d25b2248d5699af694a468e8fbaf0ce8</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.653441</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.04406600000000005</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:17.594852Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>82199f2d468a4cc1</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>0498800784d6eac428ef81724493d635d25b2248d5699af694a468e8fbaf0ce8</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.691145</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.08177000000000001</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:18.084181Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>0240d6e7d4f74e8b</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>6f1a88c65511fda132cb3c464f9d3012c11a7503cf913396060b5b8c9adc5f1b</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.653102</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.04372699999999996</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:47.373035Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>357c79d3d3b94545</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>6f1a88c65511fda132cb3c464f9d3012c11a7503cf913396060b5b8c9adc5f1b</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.641633</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.03225800000000001</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:47.847531Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>47b5ff01155d402f</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>b86d10213574fcb4e774a613f40c4fb8692dc4e3a085fafa8fe32b85c8b1f80d</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>68697</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.652267</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.07243506722689086</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:50.398494Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ8"/>
+  <autoFilter ref="A1:AJ35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ35"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4144,8 +4144,212 @@
       <c r="AI35" s="2" t="inlineStr"/>
       <c r="AJ35" s="2" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>4728e45fb2f847f9</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>f1fe994de287718d3c0fe00feaf937f6ad521dd7146bd6199a6b119f5aadc7b4</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0.10729250691244241</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:21.566885Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>9f49333d99a543d6</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.09863843192488264</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.642540Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ35"/>
+  <autoFilter ref="A1:AJ37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ37"/>
+  <dimension ref="A1:AJ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4348,8 +4348,314 @@
       <c r="AI37" s="2" t="inlineStr"/>
       <c r="AJ37" s="2" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>b06a2fafa2bc45f8</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>d69696ee60884cdbbc02198278826e438fa3acb3c76bffb0930437b7d83a7650</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.09863843192488264</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:41.929766Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>c3ade84ac94f4fac</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>aeca52ed5c92138baf9a32bd54c644f4cc5ff0cb6b6d88a1a4fea391ba441e5f</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.10729250691244241</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:08.272042Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>db3b77f98207402d</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.10729250691244241</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:42.943962Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ37"/>
+  <autoFilter ref="A1:AJ40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4654,8 +4654,1660 @@
       <c r="AI40" s="2" t="inlineStr"/>
       <c r="AJ40" s="2" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>fade7b89d1f94e83</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>4dd19640fd8669d65e0cf5399cede0ff0058dfe4bb6481bcbbc7e5d341d26579</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.10729250691244241</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:20.253708Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>0cdcc4c3af5a41ea</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.64657</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.026798136882129286</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:14.515679Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>0.630000</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0.010228</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>-1.7500</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:12.156252Z</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>c5f53b8364ee40eb</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.574697</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.1138675069124424</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:15.902210Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>4b7f1f1b5f0b4416</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>b42115c33f33aabcc9de0f93a630372616064e7907433f1bdf7964ec917a67c7</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.574902</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0.10541843192488265</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:16.186304Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>a3c20387a52a40c5</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1cd85b2e2088b327e661d25667fdd01f350a091b1e11d3fbb8c1367cbe11fa21</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.575467</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.10598343192488258</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:02:39.371107Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ad5221e97285475a</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ba67dd6aaae3eb83de1dbe1071b7a5eaa8213438dec9ededf1423df90efa991c</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.575339</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.10585543192488267</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:10:45.843691Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>736e51fcd4d049c9</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.575205</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.12475454954954945</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:20.493480Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>038616ff52084e9c</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.669254</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.059879000000000016</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:24.538997Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>14b6ec23dad648d4</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.702792</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.312167</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:26.219958Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>22899ed9f10848db</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.564054</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0.1936836296296297</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:30.958246Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>6b8cef92b90c4979</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.626628</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.17617754954954945</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:32.501687Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>1a78c2d87cf04768</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.575198</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.12474754954954947</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.028876Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>b6f1ead0523a43b3</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.669245</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.05986999999999998</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:14.218178Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>0421f84a813742f2</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.702781</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.312156</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:15.903165Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>bfa7942fda004d77</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.564051</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.19368062962962962</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:18.444919Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>7ec82a6abd5247c7</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.626622</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.1761715495495495</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.044205Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ40"/>
+  <autoFilter ref="A1:AJ56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5882,14 +5882,34 @@
       <c r="W52" s="2" t="inlineStr"/>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y52" s="2" t="inlineStr"/>
-      <c r="Z52" s="2" t="inlineStr"/>
-      <c r="AA52" s="2" t="inlineStr"/>
-      <c r="AB52" s="2" t="inlineStr"/>
-      <c r="AC52" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>0.450000</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>-0.000450</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:01.604387Z</t>
+        </is>
+      </c>
       <c r="AD52" s="2" t="inlineStr"/>
       <c r="AE52" s="2" t="inlineStr"/>
       <c r="AF52" s="2" t="inlineStr"/>
@@ -6306,8 +6326,1232 @@
       <c r="AI56" s="2" t="inlineStr"/>
       <c r="AJ56" s="2" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>86776602066549dc</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.668954</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.05957900000000005</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:17.314063Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>78c1c013d244426e</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.702279</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.311654</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:19.113124Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ab498d164d5c4102</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.563849</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.1934786296296297</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:21.604476Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>c755eab551dc4d06</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.626211</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.1856823656387665</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:22.297943Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>1656da18d3874c5c</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.668936</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.059560999999999975</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:31.989777Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>60908d0ab9594894</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.702255</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>0.31162999999999996</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:33.130398Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>bf83fd61f90a4b7b</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.563844</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.19347362962962966</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:35.676356Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>eb32ed0eac2a4f26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>0.626197</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.18566836563876654</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:36.643764Z</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>390fa7b48ffd4ff5</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>0.667906</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.058531</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:10.639279Z</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>a9614b39ffdb4de0</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>0.701767</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0.31114200000000003</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:11.760518Z</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
+      <c r="AJ66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>624bc0df69774178</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>0.563896</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.1935256296296296</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:13.229270Z</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
+      <c r="AJ67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>0206c3630fbb4d03</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>0.625458</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0.2052899327731092</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:14.786413Z</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="2" t="inlineStr"/>
+      <c r="AI68" s="2" t="inlineStr"/>
+      <c r="AJ68" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ56"/>
+  <autoFilter ref="A1:AJ68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ68"/>
+  <dimension ref="A1:AJ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7550,8 +7550,2316 @@
       <c r="AI68" s="2" t="inlineStr"/>
       <c r="AJ68" s="2" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>fe1e6ae9419b4fb9</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>0.70126</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.2914239344262295</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:42.864876Z</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="2" t="inlineStr"/>
+      <c r="AJ69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>59b319bf1a654fdf</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>0.563864</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.19349362962962968</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:44.459947Z</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="2" t="inlineStr"/>
+      <c r="AH70" s="2" t="inlineStr"/>
+      <c r="AI70" s="2" t="inlineStr"/>
+      <c r="AJ70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ff5254cd889e4153</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>0.624973</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>0.18444436563876654</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:45.562455Z</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AI71" s="2" t="inlineStr"/>
+      <c r="AJ71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>14940c36213a4fc9</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>0.695963</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>0.27579493277310924</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:49.787877Z</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="2" t="inlineStr"/>
+      <c r="AH72" s="2" t="inlineStr"/>
+      <c r="AI72" s="2" t="inlineStr"/>
+      <c r="AJ72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>54ea8d19122d4ccd</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>0.563078</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>0.20336576978417265</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:50.556034Z</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="2" t="inlineStr"/>
+      <c r="AI73" s="2" t="inlineStr"/>
+      <c r="AJ73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>60b3433b002a4837</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>0.615776</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>0.17524736563876653</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:51.720995Z</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="2" t="inlineStr"/>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>586e17e54fc4458c</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>0.695761</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.2755929327731092</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:37.569959Z</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:16.682333Z</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="2" t="inlineStr"/>
+      <c r="AJ75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>607c5b8d8403488f</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>0.563029</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>0.20331676978417268</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:38.040365Z</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1.7800</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:54.242525Z</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="2" t="inlineStr"/>
+      <c r="AJ76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>e36638e76b2d4431</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>0.615667</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>0.16521654954954945</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:38.979681Z</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="2" t="inlineStr"/>
+      <c r="AJ77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ee484ffe695a4575</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>0.615411</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>0.15458150691244243</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:13.149018Z</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>0.460000</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>-0.000829</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1.7550</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:55.521167Z</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="2" t="inlineStr"/>
+      <c r="AJ78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>31a372d6859e4c9a</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>71752</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>0.75587</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>0.13609813688212935</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:16.114368Z</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="2" t="inlineStr"/>
+      <c r="AJ79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>65566e01551e4c10</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>0.722571</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>0.37292065034965033</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:16.718069Z</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="2" t="inlineStr"/>
+      <c r="AJ80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>112634ce020c49ce</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>71752</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>0.781713</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>0.172338</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:01.720459Z</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="2" t="inlineStr"/>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="2" t="inlineStr"/>
+      <c r="AJ81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>956f85ee17504893</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>0.743939</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>0.3942886503496504</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:02.419049Z</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="2" t="inlineStr"/>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="2" t="inlineStr"/>
+      <c r="AJ82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>b2b0bbb4fbda4709</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>0.700157</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.3199288631178707</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:10.514790Z</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
+      <c r="AJ83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>0df1fef7dd3f426d</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>71752</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>0.781485</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.17210999999999999</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:21.351080Z</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>0.610000</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>0.000625</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1.2821</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:06.771362Z</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
+      <c r="AJ84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>34a8d84db2084d91</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>0.74376</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>0.39410965034965034</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:22.081076Z</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>0ee277ce5e5740c7</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>0.69991</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>0.3295396296296297</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:27.602644Z</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
+      <c r="AJ86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>adef67dbdef74cd7</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>1af3798e94d5b1473865bcb78b085884572681551a9b34a966767bcfe3a6e48f</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.743312</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.36308386311787066</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:10.020929Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>6f5733e1dff54a74</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1af3798e94d5b1473865bcb78b085884572681551a9b34a966767bcfe3a6e48f</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.699367</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.31913886311787065</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:16.500524Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>606b0df29daf4368</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.743264</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.3835517697841727</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.113763Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>9dfc962fb67444c8</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>0.699272</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>0.3190438631178707</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:59.578708Z</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ68"/>
+  <autoFilter ref="A1:AJ90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ90"/>
+  <dimension ref="A1:AJ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9858,8 +9858,212 @@
       <c r="AI90" s="2" t="inlineStr"/>
       <c r="AJ90" s="2" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>522beb13c43c4956</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>74125</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>0.637346</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>0.10682956807511734</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:13.105417Z</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
+      <c r="AJ91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>70be6ddb433145fb</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>0.698711</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>0.31848286311787066</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:13.626555Z</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
+      <c r="AJ92" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ90"/>
+  <autoFilter ref="A1:AJ92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>